--- a/Table 3 - Consolidated Comparative Table.xlsx
+++ b/Table 3 - Consolidated Comparative Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\MEU NOTEBOOK\Doutorado\PPGI UFPB\2026-2\Projeto de Tese II\Submissão Revisão\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102FE25C-0181-4FEE-9C5E-A8CB9DBD6C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD27136E-DF13-43C1-9893-C00302AC0A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="667">
   <si>
     <t>#</t>
   </si>
@@ -1159,9 +1159,6 @@
   </si>
   <si>
     <t>Magic Leap One</t>
-  </si>
-  <si>
-    <t>Passive Feedback</t>
   </si>
   <si>
     <t>HTC-Vive Pro Eye
@@ -1601,9 +1598,6 @@
     <t>Vuforia SDK</t>
   </si>
   <si>
-    <t>Presence</t>
-  </si>
-  <si>
     <t>Microsoft HoloLens2
 Unity 3D
 Robot Operating System</t>
@@ -2211,6 +2205,15 @@
   </si>
   <si>
     <t>Does it assess implementation costs?</t>
+  </si>
+  <si>
+    <t>Haptic Feedback</t>
+  </si>
+  <si>
+    <t>manipulated object</t>
+  </si>
+  <si>
+    <t>Haptic feedback</t>
   </si>
 </sst>
 </file>
@@ -2567,49 +2570,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="P1" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -2632,34 +2635,34 @@
         <v>351</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>352</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>353</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>355</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -2682,7 +2685,7 @@
         <v>356</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>357</v>
@@ -2694,13 +2697,13 @@
         <v>359</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>360</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>354</v>
@@ -2709,7 +2712,7 @@
         <v>355</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -2732,25 +2735,25 @@
         <v>361</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>362</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>363</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>354</v>
@@ -2759,7 +2762,7 @@
         <v>355</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -2782,10 +2785,10 @@
         <v>364</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>365</v>
@@ -2794,13 +2797,13 @@
         <v>366</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>354</v>
@@ -2809,7 +2812,7 @@
         <v>355</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -2832,34 +2835,34 @@
         <v>367</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>368</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M6" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>661</v>
-      </c>
       <c r="O6" s="2" t="s">
         <v>355</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -2882,25 +2885,25 @@
         <v>356</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>369</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>354</v>
@@ -2909,7 +2912,7 @@
         <v>355</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -2932,25 +2935,25 @@
         <v>351</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>354</v>
@@ -2959,7 +2962,7 @@
         <v>355</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -2982,25 +2985,25 @@
         <v>356</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>370</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>354</v>
@@ -3009,7 +3012,7 @@
         <v>355</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3032,34 +3035,34 @@
         <v>351</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>371</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>353</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>355</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3082,25 +3085,25 @@
         <v>367</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>372</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>354</v>
@@ -3109,7 +3112,7 @@
         <v>355</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -3132,25 +3135,25 @@
         <v>373</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>374</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>354</v>
@@ -3159,7 +3162,7 @@
         <v>355</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3182,25 +3185,25 @@
         <v>367</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>354</v>
@@ -3209,7 +3212,7 @@
         <v>355</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3229,28 +3232,28 @@
         <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>354</v>
@@ -3259,7 +3262,7 @@
         <v>355</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -3279,28 +3282,28 @@
         <v>43</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>354</v>
@@ -3309,7 +3312,7 @@
         <v>355</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -3332,25 +3335,25 @@
         <v>356</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>354</v>
@@ -3359,7 +3362,7 @@
         <v>355</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3382,25 +3385,25 @@
         <v>367</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>354</v>
@@ -3409,7 +3412,7 @@
         <v>355</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3429,28 +3432,28 @@
         <v>52</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>354</v>
@@ -3459,7 +3462,7 @@
         <v>355</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -3482,25 +3485,25 @@
         <v>351</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>354</v>
@@ -3509,7 +3512,7 @@
         <v>355</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -3532,25 +3535,25 @@
         <v>367</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>354</v>
@@ -3559,7 +3562,7 @@
         <v>355</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3582,34 +3585,34 @@
         <v>356</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>354</v>
+        <v>654</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>355</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="51" customHeight="1" x14ac:dyDescent="0.3">
@@ -3632,25 +3635,25 @@
         <v>367</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>354</v>
@@ -3659,7 +3662,7 @@
         <v>355</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3679,28 +3682,28 @@
         <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>354</v>
+        <v>665</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>354</v>
@@ -3709,7 +3712,7 @@
         <v>355</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -3732,25 +3735,25 @@
         <v>351</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>354</v>
@@ -3759,7 +3762,7 @@
         <v>355</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3782,25 +3785,25 @@
         <v>367</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="K25" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>354</v>
@@ -3809,7 +3812,7 @@
         <v>355</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -3832,25 +3835,25 @@
         <v>367</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>354</v>
@@ -3859,7 +3862,7 @@
         <v>355</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -3882,25 +3885,25 @@
         <v>354</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>354</v>
@@ -3909,7 +3912,7 @@
         <v>355</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -3932,25 +3935,25 @@
         <v>367</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>354</v>
@@ -3959,7 +3962,7 @@
         <v>355</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="28.8" x14ac:dyDescent="0.35">
@@ -3982,25 +3985,25 @@
         <v>351</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>354</v>
@@ -4009,7 +4012,7 @@
         <v>355</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4032,25 +4035,25 @@
         <v>367</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>354</v>
@@ -4059,7 +4062,7 @@
         <v>355</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4082,25 +4085,25 @@
         <v>367</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>354</v>
@@ -4109,7 +4112,7 @@
         <v>355</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -4132,25 +4135,25 @@
         <v>367</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H32" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="J32" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>405</v>
-      </c>
       <c r="M32" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>354</v>
@@ -4159,7 +4162,7 @@
         <v>355</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4182,25 +4185,25 @@
         <v>356</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>354</v>
@@ -4209,7 +4212,7 @@
         <v>355</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4229,28 +4232,28 @@
         <v>100</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>354</v>
+        <v>666</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>353</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>354</v>
@@ -4259,7 +4262,7 @@
         <v>355</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4282,25 +4285,25 @@
         <v>356</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H35" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>354</v>
@@ -4309,7 +4312,7 @@
         <v>355</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -4329,37 +4332,37 @@
         <v>106</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="I36" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>410</v>
-      </c>
       <c r="K36" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>355</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -4379,28 +4382,28 @@
         <v>108</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="H37" s="2" t="s">
+      <c r="I37" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>413</v>
-      </c>
       <c r="J37" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>354</v>
@@ -4409,7 +4412,7 @@
         <v>355</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -4429,28 +4432,28 @@
         <v>112</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="I38" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="J38" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="K38" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>354</v>
@@ -4459,7 +4462,7 @@
         <v>355</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4479,28 +4482,28 @@
         <v>115</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>366</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>354</v>
@@ -4509,7 +4512,7 @@
         <v>355</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4529,28 +4532,28 @@
         <v>118</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H40" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="I40" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="J40" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="J40" s="2" t="s">
-        <v>420</v>
-      </c>
       <c r="K40" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>354</v>
@@ -4559,7 +4562,7 @@
         <v>355</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4582,25 +4585,25 @@
         <v>354</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H41" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="K41" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>354</v>
@@ -4609,7 +4612,7 @@
         <v>355</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4632,25 +4635,25 @@
         <v>367</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H42" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="I42" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="J42" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="J42" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="K42" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>354</v>
@@ -4659,7 +4662,7 @@
         <v>355</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -4682,25 +4685,25 @@
         <v>367</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>354</v>
@@ -4709,7 +4712,7 @@
         <v>355</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4732,25 +4735,25 @@
         <v>367</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>354</v>
@@ -4759,7 +4762,7 @@
         <v>355</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4779,28 +4782,28 @@
         <v>130</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>354</v>
@@ -4809,7 +4812,7 @@
         <v>355</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4832,25 +4835,25 @@
         <v>373</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H46" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>354</v>
@@ -4859,7 +4862,7 @@
         <v>355</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4879,28 +4882,28 @@
         <v>136</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>354</v>
@@ -4909,7 +4912,7 @@
         <v>355</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -4929,28 +4932,28 @@
         <v>139</v>
       </c>
       <c r="F48" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>435</v>
-      </c>
       <c r="I48" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>354</v>
@@ -4959,7 +4962,7 @@
         <v>355</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -4982,25 +4985,25 @@
         <v>351</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>354</v>
@@ -5009,7 +5012,7 @@
         <v>355</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5032,25 +5035,25 @@
         <v>356</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>354</v>
@@ -5059,7 +5062,7 @@
         <v>355</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5082,25 +5085,25 @@
         <v>373</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>353</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>354</v>
@@ -5109,7 +5112,7 @@
         <v>355</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -5132,25 +5135,25 @@
         <v>367</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>354</v>
@@ -5159,7 +5162,7 @@
         <v>355</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -5179,28 +5182,28 @@
         <v>154</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="J53" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>439</v>
-      </c>
       <c r="K53" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>354</v>
@@ -5209,7 +5212,7 @@
         <v>355</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5232,25 +5235,25 @@
         <v>364</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>354</v>
@@ -5259,7 +5262,7 @@
         <v>355</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5282,25 +5285,25 @@
         <v>367</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>354</v>
@@ -5309,7 +5312,7 @@
         <v>355</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -5332,25 +5335,25 @@
         <v>367</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>363</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>354</v>
@@ -5359,7 +5362,7 @@
         <v>355</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5379,28 +5382,28 @@
         <v>169</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>354</v>
@@ -5409,7 +5412,7 @@
         <v>355</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -5432,25 +5435,25 @@
         <v>373</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>354</v>
@@ -5459,7 +5462,7 @@
         <v>355</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5482,25 +5485,25 @@
         <v>373</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>354</v>
@@ -5509,7 +5512,7 @@
         <v>355</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5529,28 +5532,28 @@
         <v>177</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>354</v>
@@ -5559,7 +5562,7 @@
         <v>355</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -5579,28 +5582,28 @@
         <v>180</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>354</v>
@@ -5609,7 +5612,7 @@
         <v>355</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5632,25 +5635,25 @@
         <v>354</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>354</v>
@@ -5659,7 +5662,7 @@
         <v>355</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -5679,28 +5682,28 @@
         <v>186</v>
       </c>
       <c r="F63" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="H63" s="2" t="s">
+      <c r="I63" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>354</v>
@@ -5709,7 +5712,7 @@
         <v>355</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -5732,25 +5735,25 @@
         <v>367</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>354</v>
@@ -5759,7 +5762,7 @@
         <v>355</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -5782,25 +5785,25 @@
         <v>367</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>354</v>
@@ -5809,7 +5812,7 @@
         <v>355</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -5829,28 +5832,28 @@
         <v>195</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I66" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>354</v>
@@ -5859,7 +5862,7 @@
         <v>355</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -5879,28 +5882,28 @@
         <v>198</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>354</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>354</v>
@@ -5909,7 +5912,7 @@
         <v>355</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5932,25 +5935,25 @@
         <v>367</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H68" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="I68" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>354</v>
@@ -5959,7 +5962,7 @@
         <v>355</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -5982,25 +5985,25 @@
         <v>367</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>354</v>
@@ -6009,7 +6012,7 @@
         <v>355</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6032,25 +6035,25 @@
         <v>367</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>354</v>
@@ -6059,7 +6062,7 @@
         <v>355</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6082,25 +6085,25 @@
         <v>367</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>354</v>
@@ -6109,7 +6112,7 @@
         <v>355</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6132,25 +6135,25 @@
         <v>367</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>354</v>
@@ -6159,7 +6162,7 @@
         <v>355</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6182,25 +6185,25 @@
         <v>356</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>354</v>
@@ -6209,7 +6212,7 @@
         <v>355</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6232,25 +6235,25 @@
         <v>367</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>354</v>
@@ -6259,7 +6262,7 @@
         <v>355</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6282,25 +6285,25 @@
         <v>356</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>354</v>
@@ -6309,7 +6312,7 @@
         <v>355</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6332,25 +6335,25 @@
         <v>351</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>354</v>
@@ -6359,7 +6362,7 @@
         <v>355</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6382,25 +6385,25 @@
         <v>359</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>354</v>
@@ -6409,7 +6412,7 @@
         <v>355</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6432,25 +6435,25 @@
         <v>351</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H78" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="I78" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>354</v>
@@ -6459,7 +6462,7 @@
         <v>355</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -6482,34 +6485,34 @@
         <v>354</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>355</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6529,28 +6532,28 @@
         <v>236</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>354</v>
@@ -6559,7 +6562,7 @@
         <v>355</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6579,28 +6582,28 @@
         <v>240</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="L81" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="M81" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>354</v>
@@ -6609,7 +6612,7 @@
         <v>355</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6632,25 +6635,25 @@
         <v>356</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H82" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="I82" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>354</v>
@@ -6659,7 +6662,7 @@
         <v>355</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6682,25 +6685,25 @@
         <v>356</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H83" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="I83" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>363</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>354</v>
@@ -6709,7 +6712,7 @@
         <v>355</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6729,28 +6732,28 @@
         <v>249</v>
       </c>
       <c r="F84" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="H84" s="2" t="s">
+      <c r="I84" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="J84" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>354</v>
@@ -6759,7 +6762,7 @@
         <v>355</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6782,25 +6785,25 @@
         <v>356</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>354</v>
@@ -6809,7 +6812,7 @@
         <v>355</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -6829,28 +6832,28 @@
         <v>254</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>354</v>
@@ -6859,7 +6862,7 @@
         <v>355</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6882,25 +6885,25 @@
         <v>354</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>362</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>354</v>
@@ -6909,7 +6912,7 @@
         <v>355</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6932,25 +6935,25 @@
         <v>356</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H88" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="J88" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="I88" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="J88" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="K88" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>354</v>
@@ -6959,7 +6962,7 @@
         <v>355</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -6982,25 +6985,25 @@
         <v>359</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>354</v>
@@ -7009,7 +7012,7 @@
         <v>355</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -7032,25 +7035,25 @@
         <v>367</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>354</v>
@@ -7059,7 +7062,7 @@
         <v>355</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7079,28 +7082,28 @@
         <v>270</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>354</v>
@@ -7109,7 +7112,7 @@
         <v>355</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7129,28 +7132,28 @@
         <v>273</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>354</v>
@@ -7159,7 +7162,7 @@
         <v>355</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7179,28 +7182,28 @@
         <v>276</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>354</v>
@@ -7209,7 +7212,7 @@
         <v>355</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -7229,28 +7232,28 @@
         <v>279</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="J94" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="K94" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>354</v>
@@ -7259,7 +7262,7 @@
         <v>355</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -7282,25 +7285,25 @@
         <v>373</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>363</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>354</v>
@@ -7309,7 +7312,7 @@
         <v>355</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7329,28 +7332,28 @@
         <v>285</v>
       </c>
       <c r="F96" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="I96" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>354</v>
@@ -7359,7 +7362,7 @@
         <v>355</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7382,25 +7385,25 @@
         <v>356</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>354</v>
@@ -7409,7 +7412,7 @@
         <v>355</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -7432,25 +7435,25 @@
         <v>351</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>354</v>
@@ -7459,7 +7462,7 @@
         <v>355</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7479,28 +7482,28 @@
         <v>294</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>354</v>
@@ -7509,7 +7512,7 @@
         <v>355</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -7529,28 +7532,28 @@
         <v>297</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>354</v>
@@ -7559,7 +7562,7 @@
         <v>355</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -7582,25 +7585,25 @@
         <v>351</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>354</v>
@@ -7609,7 +7612,7 @@
         <v>355</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7632,25 +7635,25 @@
         <v>351</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N102" s="2" t="s">
         <v>354</v>
@@ -7659,7 +7662,7 @@
         <v>355</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7679,28 +7682,28 @@
         <v>306</v>
       </c>
       <c r="F103" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="I103" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="J103" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>354</v>
@@ -7709,7 +7712,7 @@
         <v>355</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7729,28 +7732,28 @@
         <v>309</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N104" s="2" t="s">
         <v>354</v>
@@ -7759,7 +7762,7 @@
         <v>355</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7779,28 +7782,28 @@
         <v>312</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N105" s="2" t="s">
         <v>354</v>
@@ -7809,7 +7812,7 @@
         <v>355</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -7832,25 +7835,25 @@
         <v>356</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>363</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N106" s="2" t="s">
         <v>354</v>
@@ -7859,7 +7862,7 @@
         <v>355</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="107" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7882,25 +7885,25 @@
         <v>351</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H107" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="I107" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N107" s="2" t="s">
         <v>354</v>
@@ -7909,7 +7912,7 @@
         <v>355</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="108" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -7932,25 +7935,25 @@
         <v>367</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N108" s="2" t="s">
         <v>354</v>
@@ -7959,7 +7962,7 @@
         <v>355</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -7982,25 +7985,25 @@
         <v>351</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>359</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N109" s="2" t="s">
         <v>354</v>
@@ -8009,7 +8012,7 @@
         <v>355</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="110" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -8032,25 +8035,25 @@
         <v>367</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N110" s="2" t="s">
         <v>354</v>
@@ -8059,7 +8062,7 @@
         <v>355</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="111" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -8079,28 +8082,28 @@
         <v>330</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N111" s="2" t="s">
         <v>354</v>
@@ -8109,7 +8112,7 @@
         <v>355</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
@@ -8132,25 +8135,25 @@
         <v>367</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N112" s="2" t="s">
         <v>354</v>
@@ -8159,7 +8162,7 @@
         <v>355</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -8179,28 +8182,28 @@
         <v>335</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>354</v>
@@ -8209,7 +8212,7 @@
         <v>355</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -8229,28 +8232,28 @@
         <v>338</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>366</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>354</v>
@@ -8259,7 +8262,7 @@
         <v>355</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -8282,25 +8285,25 @@
         <v>367</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>354</v>
@@ -8309,7 +8312,7 @@
         <v>355</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
@@ -8332,25 +8335,25 @@
         <v>373</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>354</v>
@@ -8359,7 +8362,7 @@
         <v>355</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -8379,28 +8382,28 @@
         <v>347</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N117" s="2" t="s">
         <v>354</v>
@@ -8409,7 +8412,7 @@
         <v>355</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
@@ -8429,28 +8432,28 @@
         <v>350</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>354</v>
@@ -8459,7 +8462,7 @@
         <v>355</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
